--- a/00001/Lista_Senior_Chilcal.xlsx
+++ b/00001/Lista_Senior_Chilcal.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jorge\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\David\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5D215BF-34ED-45B6-B816-7112E89019B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BF89FA6-1583-4D49-932A-F725385A4F86}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{8D279D80-7BEE-4445-84BF-F799B163E2A2}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="21570" windowHeight="4515" xr2:uid="{8D279D80-7BEE-4445-84BF-F799B163E2A2}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -19,17 +19,6 @@
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
     </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="2"/>
@@ -44,9 +33,6 @@
     <t>N°</t>
   </si>
   <si>
-    <t>Apellido - Nombre</t>
-  </si>
-  <si>
     <t>DNI</t>
   </si>
   <si>
@@ -134,20 +120,23 @@
     <t>Club</t>
   </si>
   <si>
-    <t>Categoría</t>
-  </si>
-  <si>
-    <t>Carnet</t>
-  </si>
-  <si>
     <t>Clase</t>
+  </si>
+  <si>
+    <t>Cat</t>
+  </si>
+  <si>
+    <t>N° Carnet</t>
+  </si>
+  <si>
+    <t>Apellido y Nombre</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -530,29 +519,29 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AFB14A1C-BD01-4A25-A3B9-59EAB68D520C}">
   <dimension ref="A1:G28"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="23.77734375" defaultRowHeight="13.8" customHeight="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="23.75" defaultRowHeight="13.9" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="3.109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.5" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="9" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.5" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="9" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="4.88671875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="4.875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" ht="13.9" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
       <c r="D1" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>32</v>
@@ -561,15 +550,15 @@
         <v>31</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="13.9" customHeight="1">
       <c r="A2" s="1">
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C2" s="2">
         <v>24964781</v>
@@ -587,12 +576,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" ht="13.9" customHeight="1">
       <c r="A3" s="1">
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C3" s="2">
         <v>21608480</v>
@@ -610,12 +599,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" ht="13.9" customHeight="1">
       <c r="A4" s="1">
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C4" s="2">
         <v>25870941</v>
@@ -633,12 +622,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" ht="13.9" customHeight="1">
       <c r="A5" s="1">
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C5" s="2">
         <v>24038670</v>
@@ -656,12 +645,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" ht="13.9" customHeight="1">
       <c r="A6" s="1">
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C6" s="2">
         <v>23381868</v>
@@ -679,12 +668,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" ht="13.9" customHeight="1">
       <c r="A7" s="1">
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C7" s="2">
         <v>25915498</v>
@@ -702,12 +691,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" ht="13.9" customHeight="1">
       <c r="A8" s="1">
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C8" s="2">
         <v>28308071</v>
@@ -725,12 +714,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" ht="13.9" customHeight="1">
       <c r="A9" s="1">
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C9" s="2">
         <v>26807022</v>
@@ -748,12 +737,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" ht="13.9" customHeight="1">
       <c r="A10" s="1">
         <v>9</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C10" s="2">
         <v>22369632</v>
@@ -771,12 +760,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" ht="13.9" customHeight="1">
       <c r="A11" s="1">
         <v>10</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C11" s="2">
         <v>24511819</v>
@@ -794,12 +783,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" ht="13.9" customHeight="1">
       <c r="A12" s="1">
         <v>11</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C12" s="2">
         <v>28341195</v>
@@ -817,12 +806,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" ht="13.9" customHeight="1">
       <c r="A13" s="1">
         <v>12</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C13" s="2">
         <v>28488282</v>
@@ -840,12 +829,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" ht="13.9" customHeight="1">
       <c r="A14" s="1">
         <v>13</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C14" s="2">
         <v>28689944</v>
@@ -863,12 +852,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" ht="13.9" customHeight="1">
       <c r="A15" s="1">
         <v>14</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C15" s="2">
         <v>28904907</v>
@@ -886,12 +875,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" ht="13.9" customHeight="1">
       <c r="A16" s="1">
         <v>15</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C16" s="2">
         <v>27983051</v>
@@ -909,12 +898,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" ht="13.9" customHeight="1">
       <c r="A17" s="1">
         <v>16</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C17" s="2">
         <v>25354143</v>
@@ -932,12 +921,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" ht="13.9" customHeight="1">
       <c r="A18" s="1">
         <v>17</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C18" s="2">
         <v>23488223</v>
@@ -955,12 +944,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" ht="13.9" customHeight="1">
       <c r="A19" s="1">
         <v>18</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C19" s="2">
         <v>27983087</v>
@@ -978,12 +967,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" ht="13.9" customHeight="1">
       <c r="A20" s="1">
         <v>19</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C20" s="2">
         <v>28086643</v>
@@ -1001,12 +990,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" ht="13.9" customHeight="1">
       <c r="A21" s="1">
         <v>20</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C21" s="2">
         <v>27096427</v>
@@ -1024,12 +1013,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" ht="13.9" customHeight="1">
       <c r="A22" s="1">
         <v>21</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C22" s="2">
         <v>23630442</v>
@@ -1047,12 +1036,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" ht="13.9" customHeight="1">
       <c r="A23" s="1">
         <v>22</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C23" s="2">
         <v>24057428</v>
@@ -1070,12 +1059,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" ht="13.9" customHeight="1">
       <c r="A24" s="1">
         <v>23</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C24" s="2">
         <v>22559420</v>
@@ -1093,12 +1082,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" ht="13.9" customHeight="1">
       <c r="A25" s="1">
         <v>24</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C25" s="2">
         <v>26703076</v>
@@ -1116,12 +1105,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" ht="13.9" customHeight="1">
       <c r="A26" s="1">
         <v>25</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C26" s="2">
         <v>25634087</v>
@@ -1139,12 +1128,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="27" spans="1:7" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" ht="13.9" customHeight="1">
       <c r="A27" s="1">
         <v>26</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C27" s="2">
         <v>27096479</v>
@@ -1162,12 +1151,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="28" spans="1:7" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" ht="13.9" customHeight="1">
       <c r="A28" s="1">
         <v>27</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C28" s="2">
         <v>27096497</v>
